--- a/reports/company/双林股份_SZSE300100/双林股份_SZSE300100_Financial_Model_2026-05-18.xlsx
+++ b/reports/company/双林股份_SZSE300100/双林股份_SZSE300100_Financial_Model_2026-05-18.xlsx
@@ -14,6 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Inputs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparable Companies" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,12 +26,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.0;(#,##0.0);&quot;–&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;–&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;–&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="¥0.00"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -143,6 +150,16 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -198,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -291,6 +308,82 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="26" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="26" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -865,6 +958,1443 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Comparable Companies Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Snapshot as of May 2026 · Mkt cap &amp; EV in CNY mn (Schaeffler in EUR mn for ratio purposes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="62" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B4" s="62" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="62" t="inlineStr">
+        <is>
+          <t>Business focus</t>
+        </is>
+      </c>
+      <c r="D4" s="62" t="inlineStr">
+        <is>
+          <t>Mkt Cap (mn)</t>
+        </is>
+      </c>
+      <c r="E4" s="62" t="inlineStr">
+        <is>
+          <t>EV (mn)</t>
+        </is>
+      </c>
+      <c r="F4" s="62" t="inlineStr">
+        <is>
+          <t>EV/Rev LTM</t>
+        </is>
+      </c>
+      <c r="G4" s="62" t="inlineStr">
+        <is>
+          <t>EV/Rev NTM</t>
+        </is>
+      </c>
+      <c r="H4" s="62" t="inlineStr">
+        <is>
+          <t>EV/EBITDA LTM</t>
+        </is>
+      </c>
+      <c r="I4" s="62" t="inlineStr">
+        <is>
+          <t>EV/EBITDA NTM</t>
+        </is>
+      </c>
+      <c r="J4" s="62" t="inlineStr">
+        <is>
+          <t>P/E LTM</t>
+        </is>
+      </c>
+      <c r="K4" s="62" t="inlineStr">
+        <is>
+          <t>P/E NTM</t>
+        </is>
+      </c>
+      <c r="L4" s="62" t="inlineStr">
+        <is>
+          <t>Rev growth</t>
+        </is>
+      </c>
+      <c r="M4" s="62" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>拓普集团 Tuopu</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>SSE:601689</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>NEV body parts, T-1 to Tesla</t>
+        </is>
+      </c>
+      <c r="D5" s="63" t="n">
+        <v>102000</v>
+      </c>
+      <c r="E5" s="63" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F5" s="64" t="n">
+        <v>3.773584905660377</v>
+      </c>
+      <c r="G5" s="64" t="n">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="H5" s="64" t="n">
+        <v>23.25581395348837</v>
+      </c>
+      <c r="I5" s="64" t="n">
+        <v>18.51851851851852</v>
+      </c>
+      <c r="J5" s="64" t="n">
+        <v>34</v>
+      </c>
+      <c r="K5" s="64" t="n">
+        <v>27.56756756756757</v>
+      </c>
+      <c r="L5" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M5" s="57" t="n">
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>万向钱潮 Wanxiang</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>SZSE:000559</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Auto bearings + drive shafts</t>
+        </is>
+      </c>
+      <c r="D6" s="63" t="n">
+        <v>18800</v>
+      </c>
+      <c r="E6" s="63" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F6" s="64" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="G6" s="64" t="n">
+        <v>1.416058394160584</v>
+      </c>
+      <c r="H6" s="64" t="n">
+        <v>16.16666666666667</v>
+      </c>
+      <c r="I6" s="64" t="n">
+        <v>14.05797101449275</v>
+      </c>
+      <c r="J6" s="64" t="n">
+        <v>28.05970149253731</v>
+      </c>
+      <c r="K6" s="64" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L6" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M6" s="57" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>恒立液压 Hengli</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>SSE:601100</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Linear motion + hydraulics</t>
+        </is>
+      </c>
+      <c r="D7" s="63" t="n">
+        <v>77500</v>
+      </c>
+      <c r="E7" s="63" t="n">
+        <v>74000</v>
+      </c>
+      <c r="F7" s="64" t="n">
+        <v>7.326732673267327</v>
+      </c>
+      <c r="G7" s="64" t="n">
+        <v>6.434782608695652</v>
+      </c>
+      <c r="H7" s="64" t="n">
+        <v>25.51724137931035</v>
+      </c>
+      <c r="I7" s="64" t="n">
+        <v>22.42424242424243</v>
+      </c>
+      <c r="J7" s="64" t="n">
+        <v>35.22727272727273</v>
+      </c>
+      <c r="K7" s="64" t="n">
+        <v>31</v>
+      </c>
+      <c r="L7" s="57" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M7" s="57" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>贝斯特 Beste</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>SZSE:300580</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Precision auto parts + robot screws</t>
+        </is>
+      </c>
+      <c r="D8" s="63" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E8" s="63" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F8" s="64" t="n">
+        <v>5.088235294117647</v>
+      </c>
+      <c r="G8" s="64" t="n">
+        <v>4.119047619047619</v>
+      </c>
+      <c r="H8" s="64" t="n">
+        <v>22.17948717948718</v>
+      </c>
+      <c r="I8" s="64" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J8" s="64" t="n">
+        <v>30.35714285714286</v>
+      </c>
+      <c r="K8" s="64" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="L8" s="57" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M8" s="57" t="n">
+        <v>0.236</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>五洲新春 XCC</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>SSE:603667</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Bearings + roller screws</t>
+        </is>
+      </c>
+      <c r="D9" s="63" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E9" s="63" t="n">
+        <v>13100</v>
+      </c>
+      <c r="F9" s="64" t="n">
+        <v>3.638888888888889</v>
+      </c>
+      <c r="G9" s="64" t="n">
+        <v>2.977272727272727</v>
+      </c>
+      <c r="H9" s="64" t="n">
+        <v>29.11111111111111</v>
+      </c>
+      <c r="I9" s="64" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="J9" s="64" t="n">
+        <v>73.52941176470588</v>
+      </c>
+      <c r="K9" s="64" t="n">
+        <v>52.08333333333334</v>
+      </c>
+      <c r="L9" s="57" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M9" s="57" t="n">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>北特科技 Beite</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>SSE:603009</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Roller screws (pure-play)</t>
+        </is>
+      </c>
+      <c r="D10" s="63" t="n">
+        <v>18500</v>
+      </c>
+      <c r="E10" s="63" t="n">
+        <v>18900</v>
+      </c>
+      <c r="F10" s="64" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="G10" s="64" t="n">
+        <v>6.517241379310345</v>
+      </c>
+      <c r="H10" s="64" t="n">
+        <v>85.90909090909091</v>
+      </c>
+      <c r="I10" s="64" t="n">
+        <v>55.58823529411764</v>
+      </c>
+      <c r="J10" s="64" t="n">
+        <v>217.6470588235294</v>
+      </c>
+      <c r="K10" s="64" t="n">
+        <v>119.3548387096774</v>
+      </c>
+      <c r="L10" s="57" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M10" s="57" t="n">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>双环传动 SHRH</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>SZSE:002472</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Precision gears (robot/EV)</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E11" s="63" t="n">
+        <v>41900</v>
+      </c>
+      <c r="F11" s="64" t="n">
+        <v>3.809090909090909</v>
+      </c>
+      <c r="G11" s="64" t="n">
+        <v>3.352</v>
+      </c>
+      <c r="H11" s="64" t="n">
+        <v>23.94285714285714</v>
+      </c>
+      <c r="I11" s="64" t="n">
+        <v>20.4390243902439</v>
+      </c>
+      <c r="J11" s="64" t="n">
+        <v>37.27272727272727</v>
+      </c>
+      <c r="K11" s="64" t="n">
+        <v>30.82706766917293</v>
+      </c>
+      <c r="L11" s="57" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M11" s="57" t="n">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>鼎智科技 Dingzhi</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>BSE:873593</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Linear motors + screws</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E12" s="63" t="n">
+        <v>9150</v>
+      </c>
+      <c r="F12" s="64" t="n">
+        <v>14.07692307692308</v>
+      </c>
+      <c r="G12" s="64" t="n">
+        <v>11.02409638554217</v>
+      </c>
+      <c r="H12" s="64" t="n">
+        <v>55.45454545454545</v>
+      </c>
+      <c r="I12" s="64" t="n">
+        <v>41.59090909090909</v>
+      </c>
+      <c r="J12" s="64" t="n">
+        <v>79.16666666666667</v>
+      </c>
+      <c r="K12" s="64" t="n">
+        <v>61.29032258064516</v>
+      </c>
+      <c r="L12" s="57" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M12" s="57" t="n">
+        <v>0.265</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Schaeffler</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>FRA:SHA</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Bearings + auto (global)</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E13" s="63" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F13" s="64" t="n">
+        <v>0.4384615384615385</v>
+      </c>
+      <c r="G13" s="64" t="n">
+        <v>0.4130434782608696</v>
+      </c>
+      <c r="H13" s="64" t="n">
+        <v>3.67741935483871</v>
+      </c>
+      <c r="I13" s="64" t="n">
+        <v>3.352941176470588</v>
+      </c>
+      <c r="J13" s="64" t="n">
+        <v>6.428571428571429</v>
+      </c>
+      <c r="K13" s="64" t="n">
+        <v>5.487804878048781</v>
+      </c>
+      <c r="L13" s="57" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M13" s="57" t="n">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>STATISTICAL SUMMARY</t>
+        </is>
+      </c>
+      <c r="B15" s="65" t="n"/>
+      <c r="C15" s="65" t="n"/>
+      <c r="D15" s="65" t="n"/>
+      <c r="E15" s="65" t="n"/>
+      <c r="F15" s="65" t="n"/>
+      <c r="G15" s="65" t="n"/>
+      <c r="H15" s="65" t="n"/>
+      <c r="I15" s="65" t="n"/>
+      <c r="J15" s="65" t="n"/>
+      <c r="K15" s="65" t="n"/>
+      <c r="L15" s="65" t="n"/>
+      <c r="M15" s="65" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="F16" s="66" t="n">
+        <v>14.07692307692308</v>
+      </c>
+      <c r="G16" s="66" t="n">
+        <v>11.02409638554217</v>
+      </c>
+      <c r="H16" s="66" t="n">
+        <v>85.90909090909091</v>
+      </c>
+      <c r="I16" s="66" t="n">
+        <v>55.58823529411764</v>
+      </c>
+      <c r="J16" s="66" t="n">
+        <v>217.6470588235294</v>
+      </c>
+      <c r="K16" s="66" t="n">
+        <v>119.3548387096774</v>
+      </c>
+      <c r="L16" s="67" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M16" s="67" t="n">
+        <v>0.286</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>75th %ile</t>
+        </is>
+      </c>
+      <c r="F17" s="66" t="n">
+        <v>7.600866336633663</v>
+      </c>
+      <c r="G17" s="66" t="n">
+        <v>6.476011994002999</v>
+      </c>
+      <c r="H17" s="66" t="n">
+        <v>42.28282828282828</v>
+      </c>
+      <c r="I17" s="66" t="n">
+        <v>32.00757575757576</v>
+      </c>
+      <c r="J17" s="66" t="n">
+        <v>76.34803921568627</v>
+      </c>
+      <c r="K17" s="66" t="n">
+        <v>56.68682795698925</v>
+      </c>
+      <c r="L17" s="67" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M17" s="67" t="n">
+        <v>0.2505</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="F18" s="68" t="n">
+        <v>3.809090909090909</v>
+      </c>
+      <c r="G18" s="68" t="n">
+        <v>3.352</v>
+      </c>
+      <c r="H18" s="68" t="n">
+        <v>23.94285714285714</v>
+      </c>
+      <c r="I18" s="68" t="n">
+        <v>20.4390243902439</v>
+      </c>
+      <c r="J18" s="68" t="n">
+        <v>35.22727272727273</v>
+      </c>
+      <c r="K18" s="68" t="n">
+        <v>30.82706766917293</v>
+      </c>
+      <c r="L18" s="69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M18" s="69" t="n">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>25th %ile</t>
+        </is>
+      </c>
+      <c r="F19" s="66" t="n">
+        <v>2.595444444444444</v>
+      </c>
+      <c r="G19" s="66" t="n">
+        <v>2.196665560716656</v>
+      </c>
+      <c r="H19" s="66" t="n">
+        <v>19.17307692307692</v>
+      </c>
+      <c r="I19" s="66" t="n">
+        <v>15.67898550724638</v>
+      </c>
+      <c r="J19" s="66" t="n">
+        <v>29.20842217484009</v>
+      </c>
+      <c r="K19" s="66" t="n">
+        <v>23.89285714285714</v>
+      </c>
+      <c r="L19" s="67" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M19" s="67" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="F20" s="66" t="n">
+        <v>0.4384615384615385</v>
+      </c>
+      <c r="G20" s="66" t="n">
+        <v>0.4130434782608696</v>
+      </c>
+      <c r="H20" s="66" t="n">
+        <v>3.67741935483871</v>
+      </c>
+      <c r="I20" s="66" t="n">
+        <v>3.352941176470588</v>
+      </c>
+      <c r="J20" s="66" t="n">
+        <v>6.428571428571429</v>
+      </c>
+      <c r="K20" s="66" t="n">
+        <v>5.487804878048781</v>
+      </c>
+      <c r="L20" s="67" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M20" s="67" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="F21" s="66" t="n">
+        <v>5.28654636515664</v>
+      </c>
+      <c r="G21" s="66" t="n">
+        <v>4.370051741023671</v>
+      </c>
+      <c r="H21" s="66" t="n">
+        <v>31.6904703501551</v>
+      </c>
+      <c r="I21" s="66" t="n">
+        <v>23.90057502692536</v>
+      </c>
+      <c r="J21" s="66" t="n">
+        <v>60.18761700368373</v>
+      </c>
+      <c r="K21" s="66" t="n">
+        <v>41.71073878046217</v>
+      </c>
+      <c r="L21" s="67" t="n">
+        <v>0.1766666666666667</v>
+      </c>
+      <c r="M21" s="67" t="n">
+        <v>0.177</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>双林股份 Shuanglin</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>SZSE:300100</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>HDM + bearings + e-drive + robot screws</t>
+        </is>
+      </c>
+      <c r="D23" s="70" t="n">
+        <v>17520</v>
+      </c>
+      <c r="E23" s="70" t="n">
+        <v>18120</v>
+      </c>
+      <c r="F23" s="71" t="n">
+        <v>3.304157549234136</v>
+      </c>
+      <c r="G23" s="71" t="n">
+        <v>3.276080274814681</v>
+      </c>
+      <c r="H23" s="71" t="n">
+        <v>22.76381909547739</v>
+      </c>
+      <c r="I23" s="71" t="n">
+        <v>25.55712270803949</v>
+      </c>
+      <c r="J23" s="71" t="n">
+        <v>34.83101391650099</v>
+      </c>
+      <c r="K23" s="71" t="n">
+        <v>43.90977443609022</v>
+      </c>
+      <c r="L23" s="72" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="M23" s="72" t="n">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>IMPLIED PRICE PER SHARE FROM PEER MULTIPLES (¥)</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="n"/>
+      <c r="C25" s="65" t="n"/>
+      <c r="D25" s="65" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="65" t="n"/>
+      <c r="G25" s="65" t="n"/>
+      <c r="H25" s="65" t="n"/>
+      <c r="I25" s="65" t="n"/>
+      <c r="J25" s="65" t="n"/>
+      <c r="K25" s="65" t="n"/>
+      <c r="L25" s="65" t="n"/>
+      <c r="M25" s="65" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="inlineStr">
+        <is>
+          <t>Bear (25th %)</t>
+        </is>
+      </c>
+      <c r="C26" s="50" t="inlineStr">
+        <is>
+          <t>Base (Median)</t>
+        </is>
+      </c>
+      <c r="D26" s="50" t="inlineStr">
+        <is>
+          <t>Bull (75th %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>EV/EBITDA NTM applied to ¥709m EBITDA</t>
+        </is>
+      </c>
+      <c r="B27" s="59" t="n">
+        <v>18.00753548739329</v>
+      </c>
+      <c r="C27" s="59" t="n">
+        <v>23.78641830938857</v>
+      </c>
+      <c r="D27" s="59" t="n">
+        <v>37.83111508924865</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>EV/Revenue NTM applied to ¥5,531m revenue</t>
+        </is>
+      </c>
+      <c r="B28" s="59" t="n">
+        <v>19.77698153480107</v>
+      </c>
+      <c r="C28" s="59" t="n">
+        <v>30.71902739726027</v>
+      </c>
+      <c r="D28" s="59" t="n">
+        <v>60.30620263498388</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>P/E NTM applied to ¥399m 2026E NI</t>
+        </is>
+      </c>
+      <c r="B29" s="59" t="n">
+        <v>16.32405821917808</v>
+      </c>
+      <c r="C29" s="59" t="n">
+        <v>21.06164383561644</v>
+      </c>
+      <c r="D29" s="59" t="n">
+        <v>38.7295280048608</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>P/E forward applied to ¥519m 2027E NI</t>
+        </is>
+      </c>
+      <c r="B30" s="59" t="n">
+        <v>21.23354941291585</v>
+      </c>
+      <c r="C30" s="59" t="n">
+        <v>27.39597280873416</v>
+      </c>
+      <c r="D30" s="59" t="n">
+        <v>50.37750635218736</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Valuation Summary &amp; 12-Month Price Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="73" t="inlineStr">
+        <is>
+          <t>Current price: ¥30.00 · 12-month price target: ¥24 · Rating: SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Low (¥)</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>Base (¥)</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>High (¥)</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>Weighted (Base)</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>DCF Base (WACC=9.7%, g=2.5%)</t>
+        </is>
+      </c>
+      <c r="B5" s="59" t="n">
+        <v>14.95648635767046</v>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>16.6183181751894</v>
+      </c>
+      <c r="D5" s="59" t="n">
+        <v>18.28014999270834</v>
+      </c>
+      <c r="E5" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="59" t="n">
+        <v>3.32366363503788</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Reflects current business + base-case growth only; option value of robot wins not included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>DCF Bull (robot win materializes)</t>
+        </is>
+      </c>
+      <c r="B6" s="59" t="n">
+        <v>31.57080904977138</v>
+      </c>
+      <c r="C6" s="59" t="n">
+        <v>35.0786767219682</v>
+      </c>
+      <c r="D6" s="59" t="n">
+        <v>38.58654439416502</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="59" t="n">
+        <v>3.50786767219682</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Roller-screw量产 + corner-module scale → 28% CAGR, 18% EBITDA margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>EV/EBITDA NTM (peer median)</t>
+        </is>
+      </c>
+      <c r="B7" s="59" t="n">
+        <v>18.00753548739329</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>23.78641830938857</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>37.83111508924865</v>
+      </c>
+      <c r="E7" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F7" s="59" t="n">
+        <v>4.757283661877715</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Peer median ~11x NTM EBITDA × ¥709m → ¥-share</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>P/E NTM 2026E (peer median)</t>
+        </is>
+      </c>
+      <c r="B8" s="59" t="n">
+        <v>16.32405821917808</v>
+      </c>
+      <c r="C8" s="59" t="n">
+        <v>21.06164383561644</v>
+      </c>
+      <c r="D8" s="59" t="n">
+        <v>38.7295280048608</v>
+      </c>
+      <c r="E8" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F8" s="59" t="n">
+        <v>4.212328767123288</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Reflects depressed FY2026 NI from Q1 weakness — conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>P/E forward 2027E (peer median)</t>
+        </is>
+      </c>
+      <c r="B9" s="59" t="n">
+        <v>21.23354941291585</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>27.39597280873416</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <v>50.37750635218736</v>
+      </c>
+      <c r="E9" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="59" t="n">
+        <v>8.218791842620249</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Best 12m-forward anchor (mid-2027 NTM target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="74" t="inlineStr">
+        <is>
+          <t>Weighted Price Target</t>
+        </is>
+      </c>
+      <c r="B10" s="75" t="n">
+        <v>19.38476174170026</v>
+      </c>
+      <c r="C10" s="75" t="n">
+        <v>24.01993557885595</v>
+      </c>
+      <c r="D10" s="75" t="n">
+        <v>37.94006496243627</v>
+      </c>
+      <c r="E10" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="75" t="n">
+        <v>24.01993557885595</v>
+      </c>
+      <c r="G10" s="77" t="inlineStr">
+        <is>
+          <t>Sum of weighted bases</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Football field — valuation ranges (¥)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>DCF (Base ↔ Bull)</t>
+        </is>
+      </c>
+      <c r="B14" s="59" t="n">
+        <v>16.6183181751894</v>
+      </c>
+      <c r="C14" s="59" t="n">
+        <v>35.0786767219682</v>
+      </c>
+      <c r="D14" s="59" t="n">
+        <v>18.4603585467788</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>EV/EBITDA NTM (q1 ↔ q3)</t>
+        </is>
+      </c>
+      <c r="B15" s="59" t="n">
+        <v>18.00753548739329</v>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>37.83111508924865</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>19.82357960185536</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>EV/Revenue NTM (q1 ↔ q3)</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="n">
+        <v>19.77698153480107</v>
+      </c>
+      <c r="C16" s="59" t="n">
+        <v>60.30620263498388</v>
+      </c>
+      <c r="D16" s="59" t="n">
+        <v>40.52922110018281</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>P/E NTM 2026E (q1 ↔ q3)</t>
+        </is>
+      </c>
+      <c r="B17" s="59" t="n">
+        <v>16.32405821917808</v>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>38.7295280048608</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>22.40546978568272</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>P/E forward 2027E (q1 ↔ q3)</t>
+        </is>
+      </c>
+      <c r="B18" s="59" t="n">
+        <v>21.23354941291585</v>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>50.37750635218736</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <v>29.14395693927151</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>52-week trading range</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C19" s="59" t="n">
+        <v>49</v>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Current price (¥)</t>
+        </is>
+      </c>
+      <c r="B21" s="78" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Price target (12-mo, ¥)</t>
+        </is>
+      </c>
+      <c r="B22" s="79" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Upside / (downside) %</t>
+        </is>
+      </c>
+      <c r="B23" s="80" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="B24" s="81" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Probability-weighted scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="82" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B27" s="82" t="inlineStr">
+        <is>
+          <t>Prob.</t>
+        </is>
+      </c>
+      <c r="C27" s="82" t="inlineStr">
+        <is>
+          <t>Revenue CAGR 25–30</t>
+        </is>
+      </c>
+      <c r="D27" s="82" t="inlineStr">
+        <is>
+          <t>EBITDA mgn 30E</t>
+        </is>
+      </c>
+      <c r="E27" s="82" t="inlineStr">
+        <is>
+          <t>DCF (¥)</t>
+        </is>
+      </c>
+      <c r="F27" s="82" t="inlineStr">
+        <is>
+          <t>P/E NTM mult.</t>
+        </is>
+      </c>
+      <c r="G27" s="82" t="inlineStr">
+        <is>
+          <t>Implied price (¥)</t>
+        </is>
+      </c>
+      <c r="H27" s="82" t="inlineStr">
+        <is>
+          <t>Weighted (¥)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C28" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D28" s="57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E28" s="59" t="n">
+        <v>35.0786767219682</v>
+      </c>
+      <c r="F28" s="64" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" s="59" t="n">
+        <v>40.1420780870115</v>
+      </c>
+      <c r="H28" s="59" t="n">
+        <v>10.03551952175287</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C29" s="57" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D29" s="57" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E29" s="59" t="n">
+        <v>16.6183181751894</v>
+      </c>
+      <c r="F29" s="64" t="n">
+        <v>32</v>
+      </c>
+      <c r="G29" s="59" t="n">
+        <v>22.52833716978648</v>
+      </c>
+      <c r="H29" s="59" t="n">
+        <v>12.39058544338257</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B30" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C30" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D30" s="57" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E30" s="59" t="n">
+        <v>4.344240867500159</v>
+      </c>
+      <c r="F30" s="64" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" s="59" t="n">
+        <v>6.966640981695285</v>
+      </c>
+      <c r="H30" s="59" t="n">
+        <v>1.393328196339057</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="74" t="inlineStr">
+        <is>
+          <t>Probability-weighted target</t>
+        </is>
+      </c>
+      <c r="H31" s="83" t="n">
+        <v>23.8194331614745</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7553,4 +9083,1074 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DCF Valuation — Base Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>As of 2026-05-18 · Discount rate (WACC) = 9.67% · Terminal growth = 2.5% · CNY mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>WACC Build</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Risk-free rate (Rf, 10Y CGB)</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>PBOC 10Y constant-maturity, May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Equity risk premium (ERP)</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Damodaran A-share historical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Beta (levered)</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>5Y vs. CSI 300; auto-parts ~1.0–1.4 range</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Cost of equity (CAPM)</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>10.20%</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Rf + β × ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>PBOC 5Y LPR-spread, mid-tier corp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>After-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>3.04%</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>× (1 – 13% effective tax)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Market value of equity (mn)</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>¥17,520</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>584m diluted × ¥30.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Market value of debt (mn)</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>¥1,400</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Gross debt incl. lease + current portion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Weight of equity</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>92.6%</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Weight of debt</t>
+        </is>
+      </c>
+      <c r="B14" s="46" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>9.67%</t>
+        </is>
+      </c>
+      <c r="C15" s="8">
+        <f> W_E × COE + W_D × COD_AT</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Terminal growth (g)</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Long-run China GDP-trend (real + inflation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>DCF — Base case (CNY mn)</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>UFCF</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>PV of UFCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="B19" s="48" t="n">
+        <v>174</v>
+      </c>
+      <c r="C19" s="49" t="n">
+        <v>0.9118217301769137</v>
+      </c>
+      <c r="D19" s="48" t="n">
+        <v>158.656981050783</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="n">
+        <v>251</v>
+      </c>
+      <c r="C20" s="49" t="n">
+        <v>0.8314188676228204</v>
+      </c>
+      <c r="D20" s="48" t="n">
+        <v>208.6861357733279</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="n">
+        <v>431</v>
+      </c>
+      <c r="C21" s="49" t="n">
+        <v>0.7581057903775704</v>
+      </c>
+      <c r="D21" s="48" t="n">
+        <v>326.7435956527328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="n">
+        <v>598</v>
+      </c>
+      <c r="C22" s="49" t="n">
+        <v>0.6912573334392128</v>
+      </c>
+      <c r="D22" s="48" t="n">
+        <v>413.3718853966492</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="n">
+        <v>772</v>
+      </c>
+      <c r="C23" s="49" t="n">
+        <v>0.6303034577740227</v>
+      </c>
+      <c r="D23" s="48" t="n">
+        <v>486.5942694015455</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="50" t="inlineStr">
+        <is>
+          <t>Terminal value (Gordon)</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="n">
+        <v>13820.39847567942</v>
+      </c>
+      <c r="C24" s="49" t="n">
+        <v>0.6303034577740227</v>
+      </c>
+      <c r="D24" s="51" t="n">
+        <v>8711.044947035571</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TV formula: UFCF_2031 / (WACC – g) = ¥991 / (9.67% – 2.5%) = ¥13,820m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>Bridge to equity value</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>PV of explicit UFCF (2026E–2030E)</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="n">
+        <v>1594.052867275039</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="n">
+        <v>8711.044947035571</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Enterprise Value (EV)</t>
+        </is>
+      </c>
+      <c r="B30" s="53" t="n">
+        <v>10305.09781431061</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Less: Net debt (Q1 2026)</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Less: Minority interest</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Plus: Non-operating assets / investments</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="B34" s="53" t="n">
+        <v>9705.097814310609</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Price per share (DCF Base, ¥)</t>
+        </is>
+      </c>
+      <c r="B36" s="54" t="n">
+        <v>16.6183181751894</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Current price (¥)</t>
+        </is>
+      </c>
+      <c r="B37" s="55" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>DCF implied upside/(downside)</t>
+        </is>
+      </c>
+      <c r="B38" s="56" t="n">
+        <v>-0.44605606082702</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B39" s="56" t="n">
+        <v>0.8453141449020125</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>DCF — Scenarios</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>EV (mn)</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="inlineStr">
+        <is>
+          <t>Equity (mn)</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="inlineStr">
+        <is>
+          <t>Price/share (¥)</t>
+        </is>
+      </c>
+      <c r="H41" s="31" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="50" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="B42" s="57" t="n">
+        <v>0.0917056025369979</v>
+      </c>
+      <c r="C42" s="57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D42" s="58" t="n">
+        <v>21085.94720562943</v>
+      </c>
+      <c r="E42" s="58" t="n">
+        <v>20485.94720562943</v>
+      </c>
+      <c r="F42" s="59" t="n">
+        <v>35.0786767219682</v>
+      </c>
+      <c r="G42" s="57" t="n">
+        <v>0.1692892240656068</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="50" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B43" s="57" t="n">
+        <v>0.09670560253699791</v>
+      </c>
+      <c r="C43" s="57" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D43" s="58" t="n">
+        <v>10305.09781431061</v>
+      </c>
+      <c r="E43" s="58" t="n">
+        <v>9705.097814310609</v>
+      </c>
+      <c r="F43" s="59" t="n">
+        <v>16.6183181751894</v>
+      </c>
+      <c r="G43" s="57" t="n">
+        <v>-0.44605606082702</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="50" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B44" s="57" t="n">
+        <v>0.1067056025369979</v>
+      </c>
+      <c r="C44" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D44" s="58" t="n">
+        <v>3337.036666620093</v>
+      </c>
+      <c r="E44" s="58" t="n">
+        <v>2537.036666620093</v>
+      </c>
+      <c r="F44" s="59" t="n">
+        <v>4.344240867500159</v>
+      </c>
+      <c r="G44" s="57" t="n">
+        <v>-0.855191971083328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DCF Sensitivity — Price per share (¥)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Base case: WACC = 9.67%, g = 2.5% → ¥16.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>WACC ↓ / Terminal g →</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C4" s="60" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D4" s="60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="60" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F4" s="60" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G4" s="60" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H4" s="60" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="n">
+        <v>0.08170560253699791</v>
+      </c>
+      <c r="B5" s="59" t="n">
+        <v>16.7768305743523</v>
+      </c>
+      <c r="C5" s="59" t="n">
+        <v>19.01620139416464</v>
+      </c>
+      <c r="D5" s="59" t="n">
+        <v>20.40807085961945</v>
+      </c>
+      <c r="E5" s="59" t="n">
+        <v>22.04539569512287</v>
+      </c>
+      <c r="F5" s="59" t="n">
+        <v>23.99938347529111</v>
+      </c>
+      <c r="G5" s="59" t="n">
+        <v>26.37173386594496</v>
+      </c>
+      <c r="H5" s="59" t="n">
+        <v>29.31291679859346</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="n">
+        <v>0.08670560253699791</v>
+      </c>
+      <c r="B6" s="59" t="n">
+        <v>15.49637068621505</v>
+      </c>
+      <c r="C6" s="59" t="n">
+        <v>17.40752762003389</v>
+      </c>
+      <c r="D6" s="59" t="n">
+        <v>18.57798574410092</v>
+      </c>
+      <c r="E6" s="59" t="n">
+        <v>19.93812812307255</v>
+      </c>
+      <c r="F6" s="59" t="n">
+        <v>21.5381308188593</v>
+      </c>
+      <c r="G6" s="59" t="n">
+        <v>23.44757825898335</v>
+      </c>
+      <c r="H6" s="59" t="n">
+        <v>25.7658519076145</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="n">
+        <v>0.0917056025369979</v>
+      </c>
+      <c r="B7" s="59" t="n">
+        <v>14.36747862356906</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>16.01283078353597</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>17.00760138281985</v>
+      </c>
+      <c r="E7" s="59" t="n">
+        <v>18.15150047528122</v>
+      </c>
+      <c r="F7" s="59" t="n">
+        <v>19.48077967026658</v>
+      </c>
+      <c r="G7" s="59" t="n">
+        <v>21.04447647753604</v>
+      </c>
+      <c r="H7" s="59" t="n">
+        <v>22.91059637447949</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="n">
+        <v>0.09670560253699791</v>
+      </c>
+      <c r="B8" s="59" t="n">
+        <v>13.36526221309697</v>
+      </c>
+      <c r="C8" s="59" t="n">
+        <v>14.79271841319528</v>
+      </c>
+      <c r="D8" s="59" t="n">
+        <v>15.64601808489819</v>
+      </c>
+      <c r="E8" s="61" t="n">
+        <v>16.6183181751894</v>
+      </c>
+      <c r="F8" s="59" t="n">
+        <v>17.73637814970501</v>
+      </c>
+      <c r="G8" s="59" t="n">
+        <v>19.03563074345569</v>
+      </c>
+      <c r="H8" s="59" t="n">
+        <v>20.56400577584071</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="60" t="n">
+        <v>0.1017056025369979</v>
+      </c>
+      <c r="B9" s="59" t="n">
+        <v>12.46998042604143</v>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>13.71688788169898</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <v>14.45479894938028</v>
+      </c>
+      <c r="E9" s="59" t="n">
+        <v>15.28891043049622</v>
+      </c>
+      <c r="F9" s="59" t="n">
+        <v>16.23934636208806</v>
+      </c>
+      <c r="G9" s="59" t="n">
+        <v>17.33226446840648</v>
+      </c>
+      <c r="H9" s="59" t="n">
+        <v>18.60230070685287</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="60" t="n">
+        <v>0.1067056025369979</v>
+      </c>
+      <c r="B10" s="59" t="n">
+        <v>11.66577707721106</v>
+      </c>
+      <c r="C10" s="59" t="n">
+        <v>12.76164829108608</v>
+      </c>
+      <c r="D10" s="59" t="n">
+        <v>13.40437632046891</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <v>14.12576823695688</v>
+      </c>
+      <c r="F10" s="59" t="n">
+        <v>14.94120698869916</v>
+      </c>
+      <c r="G10" s="59" t="n">
+        <v>15.87036610857049</v>
+      </c>
+      <c r="H10" s="59" t="n">
+        <v>16.9388177442925</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="60" t="n">
+        <v>0.1117056025369979</v>
+      </c>
+      <c r="B11" s="59" t="n">
+        <v>10.93977054565215</v>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>11.90821112316346</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>12.47163381755628</v>
+      </c>
+      <c r="E11" s="59" t="n">
+        <v>13.10003762942098</v>
+      </c>
+      <c r="F11" s="59" t="n">
+        <v>13.80535217841417</v>
+      </c>
+      <c r="G11" s="59" t="n">
+        <v>14.60261757919201</v>
+      </c>
+      <c r="H11" s="59" t="n">
+        <v>15.51106890862395</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Sensitivity 2: 2030E Revenue CAGR × Terminal EBITDA margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>CAGR ↓ / Margin →</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C15" s="60" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D15" s="60" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E15" s="60" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F15" s="60" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B16" s="59" t="n">
+        <v>11.84192606604087</v>
+      </c>
+      <c r="C16" s="59" t="n">
+        <v>13.821821962397</v>
+      </c>
+      <c r="D16" s="59" t="n">
+        <v>15.3067438846641</v>
+      </c>
+      <c r="E16" s="59" t="n">
+        <v>16.79166580693119</v>
+      </c>
+      <c r="F16" s="59" t="n">
+        <v>18.77156170328732</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="60" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B17" s="59" t="n">
+        <v>13.78850124391802</v>
+      </c>
+      <c r="C17" s="59" t="n">
+        <v>16.06787024456294</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>17.77739699504663</v>
+      </c>
+      <c r="E17" s="59" t="n">
+        <v>19.48692374553032</v>
+      </c>
+      <c r="F17" s="59" t="n">
+        <v>21.76629274617524</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B18" s="59" t="n">
+        <v>15.21210232919323</v>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>17.71048688141896</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <v>19.58427529558825</v>
+      </c>
+      <c r="E18" s="59" t="n">
+        <v>21.45806370975754</v>
+      </c>
+      <c r="F18" s="59" t="n">
+        <v>23.95644826198327</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="60" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="B19" s="59" t="n">
+        <v>17.96538216043477</v>
+      </c>
+      <c r="C19" s="59" t="n">
+        <v>20.88734822515919</v>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>23.07882277370251</v>
+      </c>
+      <c r="E19" s="59" t="n">
+        <v>25.27029732224582</v>
+      </c>
+      <c r="F19" s="59" t="n">
+        <v>28.19226338697025</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="60" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="B20" s="59" t="n">
+        <v>20.15129612650168</v>
+      </c>
+      <c r="C20" s="59" t="n">
+        <v>23.40955664754408</v>
+      </c>
+      <c r="D20" s="59" t="n">
+        <v>25.85325203832589</v>
+      </c>
+      <c r="E20" s="59" t="n">
+        <v>28.29694742910769</v>
+      </c>
+      <c r="F20" s="59" t="n">
+        <v>31.5552079501501</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="60" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="B21" s="59" t="n">
+        <v>23.0352843003929</v>
+      </c>
+      <c r="C21" s="59" t="n">
+        <v>26.73723530972625</v>
+      </c>
+      <c r="D21" s="59" t="n">
+        <v>29.51369856672628</v>
+      </c>
+      <c r="E21" s="59" t="n">
+        <v>32.29016182372629</v>
+      </c>
+      <c r="F21" s="59" t="n">
+        <v>35.99211283305966</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="60" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="B22" s="59" t="n">
+        <v>26.22522961365792</v>
+      </c>
+      <c r="C22" s="59" t="n">
+        <v>30.41794144041667</v>
+      </c>
+      <c r="D22" s="59" t="n">
+        <v>33.56247531048573</v>
+      </c>
+      <c r="E22" s="59" t="n">
+        <v>36.70700918055479</v>
+      </c>
+      <c r="F22" s="59" t="n">
+        <v>40.89972100731355</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B5:H11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00FFC7CE"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:F22">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00FFC7CE"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00C6EFCE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>